--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/JUNTA MAGNETO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/JUNTA MAGNETO.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JUNTA MAG VEDAMOTOS CG TITAN FAN150 2004/ CRF150F 2012/ BROS NXR160 2006</t>
+          <t>JUNTA MAGNETO VEDAMOTOS CG TITAN FAN150 2004/ CRF150F 2012/ BROS NXR160 2006</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +457,11 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JUNTA MAG VEDAMOTOS YBR125 XTZ125 2011 A 2017</t>
+          <t>JUNTA MAGNETO VEDAMOTOS YBR125 XTZ125 2011 A 2017</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -478,7 +482,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -491,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JUNTA MAG VEDAMOTOS FAN CG125/ TITAN 2000/ NXR BROS125 2003 A 2005</t>
+          <t>JUNTA MAGNETO VEDAMOTOS FAN CG125/ TITAN 2000/ NXR BROS125 2003 A 2005</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -499,7 +507,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -512,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JUNTA MAG VEDAMOTOS TWISTER CBX250/ TORNADO XR250</t>
+          <t>JUNTA MAGNETO VEDAMOTOS TWISTER CBX250/ TORNADO XR250</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -520,7 +532,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +557,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -562,7 +582,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -575,7 +599,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JUNTA MAG VALFLEX SUSUKI YES125 2002 A 2008 67395</t>
+          <t>JUNTA MAGNETO VALFLEX SUSUKI YES125 2002 A 2008 67395</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -583,7 +607,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -596,7 +624,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JUNTA MAG BRAVIC FAZER250/ LANDER XTZ250 2016 2019 BMA48507</t>
+          <t>JUNTA MAGNETO BRAVIC FAZER250/ LANDER XTZ250 2016 2019 BMA48507</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -604,7 +632,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -617,7 +649,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JUNTA MAG PEÇA+ FAZER150/ CROSSER XTZ150/ FACTOR150</t>
+          <t>JUNTA MAGNETO PEÇA+ FAZER150/ CROSSER XTZ150/ FACTOR150</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -642,7 +674,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JUNTA MAG PEÇA+ TWISTER 2016</t>
+          <t>JUNTA MAGNETO PEÇA+ TWISTER 2016</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -667,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JUNTA MAG BRAVIC FAZER150/ XTZ150 CROSSER 2016 A 2019 BMA48506</t>
+          <t>JUNTA MAGNETO BRAVIC FAZER150/ XTZ150 CROSSER 2016 A 2019 BMA48506</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/JUNTA MAGNETO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/JUNTA MAGNETO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -705,11 +650,6 @@
       <c r="D12" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
     </row>
